--- a/research/traditional_assets/database/data/pakistan/pakistan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ17"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.108</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E2">
-        <v>0.212</v>
+        <v>-0.0004500000000000007</v>
       </c>
       <c r="G2">
-        <v>0.002744805469567734</v>
+        <v>0.003199620300813407</v>
       </c>
       <c r="H2">
-        <v>0.002744805469567734</v>
+        <v>0.003199620300813407</v>
       </c>
       <c r="I2">
-        <v>0.001935319894280901</v>
+        <v>0.003649694767679743</v>
       </c>
       <c r="J2">
-        <v>0.001541203849753931</v>
+        <v>0.002769716018934144</v>
       </c>
       <c r="K2">
-        <v>64.736</v>
+        <v>27.58</v>
       </c>
       <c r="L2">
-        <v>0.360421352693584</v>
+        <v>0.2256918872031554</v>
       </c>
       <c r="M2">
-        <v>7.64356</v>
+        <v>11.4524</v>
       </c>
       <c r="N2">
-        <v>0.03142523537392591</v>
+        <v>0.06300004400827357</v>
       </c>
       <c r="O2">
-        <v>0.1180727879387049</v>
+        <v>0.4152429296591733</v>
       </c>
       <c r="P2">
-        <v>6.20356</v>
+        <v>11.4524</v>
       </c>
       <c r="Q2">
-        <v>0.0255049130452658</v>
+        <v>0.06300004400827357</v>
       </c>
       <c r="R2">
-        <v>0.09582859614434007</v>
+        <v>0.4152429296591733</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1883938897581755</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>211.729</v>
+        <v>150.255</v>
       </c>
       <c r="V2">
-        <v>0.8704888377256095</v>
+        <v>0.8265578928838622</v>
       </c>
       <c r="W2">
-        <v>0.06837209302325581</v>
+        <v>0.01138686131386861</v>
       </c>
       <c r="X2">
-        <v>0.0642844050224283</v>
+        <v>0.14281155891357</v>
       </c>
       <c r="Y2">
-        <v>0.004087688000827511</v>
+        <v>-0.1314246975997014</v>
       </c>
       <c r="Z2">
-        <v>0.3154081514730069</v>
+        <v>0.1453636649124977</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06402222787107405</v>
+        <v>0.1346535148184695</v>
       </c>
       <c r="AC2">
-        <v>-0.06809188616763524</v>
+        <v>-0.1346535148184695</v>
       </c>
       <c r="AD2">
-        <v>544.6</v>
+        <v>384.567</v>
       </c>
       <c r="AE2">
-        <v>0.01196661574209391</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>544.6119666157421</v>
+        <v>384.567</v>
       </c>
       <c r="AG2">
-        <v>332.8829666157421</v>
+        <v>234.312</v>
       </c>
       <c r="AH2">
-        <v>0.6912705716289524</v>
+        <v>0.6790259044302914</v>
       </c>
       <c r="AI2">
-        <v>0.4907391318440012</v>
+        <v>0.4699194005630719</v>
       </c>
       <c r="AJ2">
-        <v>0.5778084957385964</v>
+        <v>0.5631200492194109</v>
       </c>
       <c r="AK2">
-        <v>0.3706731017096916</v>
+        <v>0.3507071408579088</v>
       </c>
       <c r="AL2">
-        <v>0.355</v>
+        <v>0.458</v>
       </c>
       <c r="AM2">
-        <v>0.271</v>
+        <v>0.41</v>
       </c>
       <c r="AN2">
-        <v>1358.104738154613</v>
+        <v>789.6652977412731</v>
       </c>
       <c r="AO2">
-        <v>0.9492957746478873</v>
+        <v>0.9737991266375544</v>
       </c>
       <c r="AP2">
-        <v>830.1320863235463</v>
+        <v>481.1334702258727</v>
       </c>
       <c r="AQ2">
-        <v>1.243542435424354</v>
+        <v>1.08780487804878</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIPL Securities Limited (KASE:BIPLS)</t>
+          <t>First Al-Noor Modaraba (KASE:FANM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.196</v>
+        <v>-0.008880000000000001</v>
       </c>
       <c r="E3">
-        <v>0.471</v>
+        <v>-0.053</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3152173913043478</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3152173913043478</v>
       </c>
       <c r="I3">
-        <v>0.002762155430099276</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="J3">
-        <v>0.001903214193126468</v>
+        <v>0.1994884910485933</v>
       </c>
       <c r="K3">
-        <v>1.06</v>
+        <v>0.011</v>
       </c>
       <c r="L3">
-        <v>0.2760416666666667</v>
+        <v>0.05978260869565217</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,67 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.05</v>
+        <v>0.465</v>
       </c>
       <c r="V3">
-        <v>0.2095435684647303</v>
+        <v>1.01528384279476</v>
       </c>
       <c r="W3">
-        <v>0.2260127931769723</v>
+        <v>0.006874999999999999</v>
       </c>
       <c r="X3">
-        <v>0.06376146763937311</v>
+        <v>0.1248577167703053</v>
       </c>
       <c r="Y3">
-        <v>0.1622513255375992</v>
+        <v>-0.1179827167703053</v>
       </c>
       <c r="Z3">
-        <v>9.553032141514407</v>
+        <v>0.149959250203749</v>
       </c>
       <c r="AA3">
-        <v>0.01818146635912356</v>
+        <v>0.02991514454192434</v>
       </c>
       <c r="AB3">
-        <v>0.06367123133192913</v>
+        <v>0.1248577167703053</v>
       </c>
       <c r="AC3">
-        <v>-0.04548976497280557</v>
+        <v>-0.094942572228381</v>
       </c>
       <c r="AD3">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.01196661574209391</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9219666157420939</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4.128033384257906</v>
+        <v>-0.465</v>
       </c>
       <c r="AH3">
-        <v>0.03684628909871761</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1424554035089655</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2066913821598395</v>
+        <v>66.42857142857137</v>
       </c>
       <c r="AK3">
-        <v>-2.903045218191408</v>
+        <v>-0.607843137254902</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-317.5410295583005</v>
+        <v>-8.017241379310345</v>
+      </c>
+      <c r="AQ3">
+        <v>-17.33333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -847,28 +850,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0552</v>
+        <v>0.137</v>
       </c>
       <c r="E4">
-        <v>-0.196</v>
+        <v>0.0429</v>
       </c>
       <c r="G4">
-        <v>0.7072864321608039</v>
+        <v>0.4870748299319728</v>
       </c>
       <c r="H4">
-        <v>0.7072864321608039</v>
+        <v>0.4870748299319728</v>
       </c>
       <c r="I4">
-        <v>0.5251256281407035</v>
+        <v>0.5700680272108843</v>
       </c>
       <c r="J4">
-        <v>0.3452880842569009</v>
+        <v>0.3126179504059688</v>
       </c>
       <c r="K4">
-        <v>0.096</v>
+        <v>0.034</v>
       </c>
       <c r="L4">
-        <v>0.1206030150753769</v>
+        <v>0.04625850340136055</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.882</v>
+        <v>0.327</v>
       </c>
       <c r="V4">
-        <v>0.341860465116279</v>
+        <v>0.2069620253164557</v>
       </c>
       <c r="W4">
-        <v>0.02167042889390519</v>
+        <v>0.007798165137614678</v>
       </c>
       <c r="X4">
-        <v>0.09832705060642981</v>
+        <v>0.3483790193538364</v>
       </c>
       <c r="Y4">
-        <v>-0.07665662171252462</v>
+        <v>-0.3405808542162217</v>
       </c>
       <c r="Z4">
-        <v>0.08381594187638203</v>
+        <v>0.1180154142581888</v>
       </c>
       <c r="AA4">
-        <v>0.0289406460006837</v>
+        <v>0.03689373692170633</v>
       </c>
       <c r="AB4">
-        <v>0.07922947384084467</v>
+        <v>0.1587312738620833</v>
       </c>
       <c r="AC4">
-        <v>-0.05028882784016096</v>
+        <v>-0.1218375369403769</v>
       </c>
       <c r="AD4">
-        <v>2.75</v>
+        <v>5.78</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.75</v>
+        <v>5.78</v>
       </c>
       <c r="AG4">
-        <v>1.868</v>
+        <v>5.453</v>
       </c>
       <c r="AH4">
-        <v>0.5159474671669794</v>
+        <v>0.7853260869565217</v>
       </c>
       <c r="AI4">
-        <v>0.3867791842475387</v>
+        <v>0.6443701226309921</v>
       </c>
       <c r="AJ4">
-        <v>0.4199640287769784</v>
+        <v>0.7753448030712357</v>
       </c>
       <c r="AK4">
-        <v>0.2999357739242132</v>
+        <v>0.6309151914844383</v>
       </c>
       <c r="AL4">
-        <v>0.355</v>
+        <v>0.458</v>
       </c>
       <c r="AM4">
-        <v>0.355</v>
+        <v>0.458</v>
       </c>
       <c r="AN4">
-        <v>5.952380952380952</v>
+        <v>12.75938189845475</v>
       </c>
       <c r="AO4">
-        <v>1.177464788732394</v>
+        <v>0.9148471615720524</v>
       </c>
       <c r="AP4">
-        <v>4.043290043290042</v>
+        <v>12.03752759381898</v>
       </c>
       <c r="AQ4">
-        <v>1.177464788732394</v>
+        <v>0.9148471615720524</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dawood Equities Limited (KASE:DEL)</t>
+          <t>B.F. Modaraba (KASE:BFMOD)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,10 +981,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.457</v>
-      </c>
-      <c r="E5">
-        <v>0.597</v>
+        <v>-0.249</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,58 +996,61 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.182</v>
+        <v>-0.064</v>
       </c>
       <c r="L5">
-        <v>0.2182254196642686</v>
+        <v>-2.56</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.016</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1300813008130081</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>-0.25</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.016</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1300813008130081</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>-0.25</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.08799999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="V5">
-        <v>0.0411214953271028</v>
+        <v>0.08130081300813008</v>
       </c>
       <c r="W5">
-        <v>0.1181818181818182</v>
+        <v>-0.07729468599033817</v>
       </c>
       <c r="X5">
-        <v>0.06247469179582767</v>
+        <v>0.1248577167703053</v>
       </c>
       <c r="Y5">
-        <v>0.05570712638599051</v>
+        <v>-0.2021524027606435</v>
       </c>
       <c r="Z5">
-        <v>0.5559999999999999</v>
+        <v>0.03075030750307503</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06247469179582767</v>
+        <v>0.1248577167703053</v>
       </c>
       <c r="AC5">
-        <v>-0.06247469179582767</v>
+        <v>-0.1248577167703053</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1059,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.08799999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1068,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.0428849902534113</v>
+        <v>-0.08849557522123894</v>
       </c>
       <c r="AK5">
-        <v>-0.05459057071960298</v>
+        <v>-0.01968503937007874</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Security Investment Bank Limited (KASE:SIBL)</t>
+          <t>AKD Securities Limited (KASE:AKDSL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,7 +1100,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.108</v>
+        <v>0.063</v>
+      </c>
+      <c r="E6">
+        <v>0.15</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,82 +1118,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.294</v>
+        <v>0.706</v>
       </c>
       <c r="L6">
-        <v>0.7696335078534031</v>
+        <v>0.2417808219178082</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.6734</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.03669736842105263</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>2.370254957507082</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1.6734</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.03669736842105263</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>2.370254957507082</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.06900000000000001</v>
+        <v>4.28</v>
       </c>
       <c r="V6">
-        <v>0.04285714285714286</v>
+        <v>0.09385964912280702</v>
       </c>
       <c r="W6">
-        <v>0.06837209302325581</v>
+        <v>0.1281306715063521</v>
       </c>
       <c r="X6">
-        <v>0.06247469179582767</v>
+        <v>0.1259765614498509</v>
       </c>
       <c r="Y6">
-        <v>0.005897401227428135</v>
+        <v>0.002154110056501207</v>
       </c>
       <c r="Z6">
-        <v>0.09037142181215994</v>
+        <v>41.71428571428607</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06247469179582767</v>
+        <v>0.1255848260087029</v>
       </c>
       <c r="AC6">
-        <v>-0.06247469179582767</v>
+        <v>-0.1255848260087029</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.835</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.835</v>
       </c>
       <c r="AG6">
-        <v>-0.06900000000000001</v>
+        <v>-3.445</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.01798212555184667</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1435941530524505</v>
       </c>
       <c r="AJ6">
-        <v>-0.04477611940298507</v>
+        <v>-0.08172221563278378</v>
       </c>
       <c r="AK6">
-        <v>-0.01589495507947478</v>
+        <v>-2.244299674267101</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.F. Modaraba (KASE:BFMOD)</t>
+          <t>Escorts Investment Bank Limited (KASE:ESBL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,10 +1222,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0444</v>
-      </c>
-      <c r="E7">
-        <v>-0.124</v>
+        <v>0.537</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,85 +1237,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.025</v>
+        <v>-0.864</v>
       </c>
       <c r="L7">
-        <v>0.373134328358209</v>
+        <v>-2.420168067226891</v>
       </c>
       <c r="M7">
-        <v>0.02256</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.07971731448763252</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.9024</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0.02256</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.07971731448763252</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.9024</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0.015</v>
+        <v>0.179</v>
       </c>
       <c r="V7">
-        <v>0.0530035335689046</v>
+        <v>0.07047244094488189</v>
       </c>
       <c r="W7">
-        <v>0.03117206982543641</v>
+        <v>-0.1774127310061601</v>
       </c>
       <c r="X7">
-        <v>0.06247469179582767</v>
+        <v>0.1306069821083971</v>
       </c>
       <c r="Y7">
-        <v>-0.03130262197039126</v>
+        <v>-0.3080197131145572</v>
       </c>
       <c r="Z7">
-        <v>0.0975254730713246</v>
+        <v>0.07344167866694096</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06247469179582767</v>
+        <v>0.1283352235971319</v>
       </c>
       <c r="AC7">
-        <v>-0.06247469179582767</v>
+        <v>-0.1283352235971319</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="AG7">
-        <v>-0.015</v>
+        <v>0.06</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.08600215905001798</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.07916528651871481</v>
       </c>
       <c r="AJ7">
-        <v>-0.05597014925373135</v>
+        <v>0.02307692307692307</v>
       </c>
       <c r="AK7">
-        <v>-0.01845018450184502</v>
+        <v>0.02112676056338028</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1335,10 +1338,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.106</v>
+        <v>-0.07629999999999999</v>
       </c>
       <c r="E8">
-        <v>0.212</v>
+        <v>-0.274</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,85 +1356,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2.76</v>
+        <v>0.156</v>
       </c>
       <c r="L8">
-        <v>0.396551724137931</v>
+        <v>0.06473029045643153</v>
       </c>
       <c r="M8">
-        <v>3.05</v>
+        <v>0.601</v>
       </c>
       <c r="N8">
-        <v>0.232824427480916</v>
+        <v>0.04926229508196722</v>
       </c>
       <c r="O8">
-        <v>1.105072463768116</v>
+        <v>3.852564102564103</v>
       </c>
       <c r="P8">
-        <v>1.61</v>
+        <v>0.601</v>
       </c>
       <c r="Q8">
-        <v>0.1229007633587786</v>
+        <v>0.04926229508196722</v>
       </c>
       <c r="R8">
-        <v>0.5833333333333334</v>
+        <v>3.852564102564103</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.4721311475409836</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>11.8</v>
+        <v>6.24</v>
       </c>
       <c r="V8">
-        <v>0.900763358778626</v>
+        <v>0.5114754098360657</v>
       </c>
       <c r="W8">
-        <v>0.1916666666666667</v>
+        <v>0.01138686131386861</v>
       </c>
       <c r="X8">
-        <v>0.06375850977960773</v>
+        <v>0.1392314716443095</v>
       </c>
       <c r="Y8">
-        <v>0.1279081568870589</v>
+        <v>-0.1278446103304409</v>
       </c>
       <c r="Z8">
-        <v>2.598954443614637</v>
+        <v>1.004166666666667</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06358905360239847</v>
+        <v>0.1325583649376931</v>
       </c>
       <c r="AC8">
-        <v>-0.06358905360239847</v>
+        <v>-0.1325583649376931</v>
       </c>
       <c r="AD8">
-        <v>0.5</v>
+        <v>2.87</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.5</v>
+        <v>2.87</v>
       </c>
       <c r="AG8">
-        <v>-11.3</v>
+        <v>-3.37</v>
       </c>
       <c r="AH8">
-        <v>0.03676470588235294</v>
+        <v>0.1904445919044459</v>
       </c>
       <c r="AI8">
-        <v>0.0352112676056338</v>
+        <v>0.2285031847133758</v>
       </c>
       <c r="AJ8">
-        <v>-6.277777777777782</v>
+        <v>-0.3816534541336354</v>
       </c>
       <c r="AK8">
-        <v>-4.708333333333337</v>
+        <v>-0.5332278481012659</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Escorts Investment Bank Limited (KASE:ESBL)</t>
+          <t>Dawood Equities Limited (KASE:DEL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1456,6 +1459,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0935</v>
+      </c>
+      <c r="E9">
+        <v>0.598</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1469,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-0.392</v>
+        <v>0.024</v>
       </c>
       <c r="L9">
-        <v>-0.7313432835820896</v>
+        <v>0.04771371769383698</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1481,7 +1490,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1490,61 +1499,61 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="V9">
-        <v>0.05507042253521127</v>
+        <v>0.5434439178515007</v>
       </c>
       <c r="W9">
-        <v>-0.0725925925925926</v>
+        <v>0.01411764705882353</v>
       </c>
       <c r="X9">
-        <v>0.0642844050224283</v>
+        <v>0.14281155891357</v>
       </c>
       <c r="Y9">
-        <v>-0.1368769976150209</v>
+        <v>-0.1286939118547465</v>
       </c>
       <c r="Z9">
-        <v>0.09032692955847658</v>
+        <v>0.3120347394540943</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06402222787107405</v>
+        <v>0.1346535148184695</v>
       </c>
       <c r="AC9">
-        <v>-0.06402222787107405</v>
+        <v>-0.1346535148184695</v>
       </c>
       <c r="AD9">
-        <v>0.382</v>
+        <v>0.186</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.382</v>
+        <v>0.186</v>
       </c>
       <c r="AG9">
-        <v>-0.009000000000000008</v>
+        <v>-0.158</v>
       </c>
       <c r="AH9">
-        <v>0.05105586741512965</v>
+        <v>0.2271062271062271</v>
       </c>
       <c r="AI9">
-        <v>0.07273419649657274</v>
+        <v>0.1313559322033898</v>
       </c>
       <c r="AJ9">
-        <v>-0.001269214497250037</v>
+        <v>-0.3326315789473683</v>
       </c>
       <c r="AK9">
-        <v>-0.001851470890763219</v>
+        <v>-0.1473880597014925</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1569,8 +1578,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="E10">
-        <v>0.259</v>
+      <c r="D10">
+        <v>0.39</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.6919999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="L10">
-        <v>0.8894601542416452</v>
+        <v>0.5581947743467933</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1612,55 +1621,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.536</v>
+        <v>0.093</v>
       </c>
       <c r="V10">
-        <v>0.1887323943661972</v>
+        <v>0.0636986301369863</v>
       </c>
       <c r="W10">
-        <v>0.3661375661375662</v>
+        <v>0.0914396887159533</v>
       </c>
       <c r="X10">
-        <v>0.06950983352750809</v>
+        <v>0.1542782566138413</v>
       </c>
       <c r="Y10">
-        <v>0.296627732610058</v>
+        <v>-0.06283856789788801</v>
       </c>
       <c r="Z10">
-        <v>0.3225538971807629</v>
+        <v>0.1601978691019787</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06809188616763524</v>
+        <v>0.1379995951173265</v>
       </c>
       <c r="AC10">
-        <v>-0.06809188616763524</v>
+        <v>-0.1379995951173265</v>
       </c>
       <c r="AD10">
-        <v>0.594</v>
+        <v>0.703</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.594</v>
+        <v>0.703</v>
       </c>
       <c r="AG10">
-        <v>0.05799999999999994</v>
+        <v>0.61</v>
       </c>
       <c r="AH10">
-        <v>0.1729761211415259</v>
+        <v>0.3250115580212667</v>
       </c>
       <c r="AI10">
-        <v>0.1877370417193426</v>
+        <v>0.2481468408048006</v>
       </c>
       <c r="AJ10">
-        <v>0.02001380262249826</v>
+        <v>0.2946859903381643</v>
       </c>
       <c r="AK10">
-        <v>0.02207001522070013</v>
+        <v>0.2226277372262774</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,10 +1695,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.189</v>
+        <v>0.0301</v>
       </c>
       <c r="E11">
-        <v>0.205</v>
+        <v>-0.0126</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1704,28 +1713,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>9.449999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="L11">
-        <v>0.8076923076923077</v>
+        <v>0.5706214689265536</v>
       </c>
       <c r="M11">
-        <v>0.864</v>
+        <v>2.89</v>
       </c>
       <c r="N11">
-        <v>0.05366459627329192</v>
+        <v>0.2580357142857143</v>
       </c>
       <c r="O11">
-        <v>0.09142857142857143</v>
+        <v>0.7153465346534653</v>
       </c>
       <c r="P11">
-        <v>0.864</v>
+        <v>2.89</v>
       </c>
       <c r="Q11">
-        <v>0.05366459627329192</v>
+        <v>0.2580357142857143</v>
       </c>
       <c r="R11">
-        <v>0.09142857142857143</v>
+        <v>0.7153465346534653</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1734,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>7.04</v>
+        <v>5.26</v>
       </c>
       <c r="V11">
-        <v>0.4372670807453416</v>
+        <v>0.4696428571428571</v>
       </c>
       <c r="W11">
-        <v>0.4237668161434977</v>
+        <v>0.12625</v>
       </c>
       <c r="X11">
-        <v>0.0788957604315914</v>
+        <v>0.1903230513134305</v>
       </c>
       <c r="Y11">
-        <v>0.3448710557119063</v>
+        <v>-0.06407305131343047</v>
       </c>
       <c r="Z11">
-        <v>0.5060553633217992</v>
+        <v>0.2964824120603015</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07241799894734625</v>
+        <v>0.1457724292326146</v>
       </c>
       <c r="AC11">
-        <v>-0.07241799894734625</v>
+        <v>-0.1457724292326146</v>
       </c>
       <c r="AD11">
-        <v>7.86</v>
+        <v>12</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>7.86</v>
+        <v>12</v>
       </c>
       <c r="AG11">
-        <v>0.8200000000000003</v>
+        <v>6.74</v>
       </c>
       <c r="AH11">
-        <v>0.3280467445742905</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="AI11">
-        <v>0.2235494880546075</v>
+        <v>0.3183023872679045</v>
       </c>
       <c r="AJ11">
-        <v>0.04846335697399529</v>
+        <v>0.3756967670011149</v>
       </c>
       <c r="AK11">
-        <v>0.02916073968705549</v>
+        <v>0.2077681874229347</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1808,10 +1817,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.71</v>
+        <v>0.12</v>
       </c>
       <c r="E12">
-        <v>0.277</v>
+        <v>0.0117</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,28 +1835,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>39.7</v>
+        <v>17</v>
       </c>
       <c r="L12">
-        <v>0.9341176470588236</v>
+        <v>0.7172995780590717</v>
       </c>
       <c r="M12">
-        <v>3.59</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>0.04330518697225572</v>
+        <v>0.0966183574879227</v>
       </c>
       <c r="O12">
-        <v>0.09042821158690176</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="P12">
-        <v>3.59</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>0.04330518697225572</v>
+        <v>0.0966183574879227</v>
       </c>
       <c r="R12">
-        <v>0.09042821158690176</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1856,55 +1865,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>20.5</v>
+        <v>12.7</v>
       </c>
       <c r="V12">
-        <v>0.2472858866103739</v>
+        <v>0.2045088566827697</v>
       </c>
       <c r="W12">
-        <v>0.2554697554697555</v>
+        <v>0.08952080042127435</v>
       </c>
       <c r="X12">
-        <v>0.09128239038964761</v>
+        <v>0.1946171274707948</v>
       </c>
       <c r="Y12">
-        <v>0.1641873650801079</v>
+        <v>-0.1050963270495205</v>
       </c>
       <c r="Z12">
-        <v>0.1941614509571017</v>
+        <v>0.09922960978060627</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0749455888581384</v>
+        <v>0.1478512322057711</v>
       </c>
       <c r="AC12">
-        <v>-0.0749455888581384</v>
+        <v>-0.1478512322057711</v>
       </c>
       <c r="AD12">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AG12">
-        <v>50.5</v>
+        <v>58.2</v>
       </c>
       <c r="AH12">
-        <v>0.4613385315139701</v>
+        <v>0.5330827067669174</v>
       </c>
       <c r="AI12">
-        <v>0.2652222637280538</v>
+        <v>0.2891517128874388</v>
       </c>
       <c r="AJ12">
-        <v>0.3785607196401799</v>
+        <v>0.483790523690773</v>
       </c>
       <c r="AK12">
-        <v>0.2042880258899676</v>
+        <v>0.2503225806451613</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1921,7 +1930,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pervez Ahmed Consultancy Services Limited (KASE:PASL)</t>
+          <t>EFG Hermes Pakistan Limited (KASE:EFGH)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1929,86 +1938,107 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
       <c r="K13">
-        <v>-0.002</v>
+        <v>-0.303</v>
+      </c>
+      <c r="L13">
+        <v>-0.5343915343915344</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.0008403361344537816</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0.0033003300330033</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.0008403361344537816</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0.0033003300330033</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.4672268907563026</v>
       </c>
       <c r="W13">
-        <v>0.0005970149253731343</v>
+        <v>-0.3</v>
       </c>
       <c r="X13">
-        <v>0.08779514859703656</v>
+        <v>0.3209969935975508</v>
       </c>
       <c r="Y13">
-        <v>-0.08719813367166343</v>
+        <v>-0.6209969935975508</v>
       </c>
       <c r="Z13">
-        <v>-0</v>
+        <v>0.1493284171714511</v>
       </c>
       <c r="AA13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07549241564463069</v>
+        <v>0.1577456375497414</v>
       </c>
       <c r="AC13">
-        <v>-0.07549241564463069</v>
+        <v>-0.1577456375497414</v>
       </c>
       <c r="AD13">
-        <v>0.8129999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.8129999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="AG13">
-        <v>0.8129999999999999</v>
+        <v>3.264</v>
       </c>
       <c r="AH13">
-        <v>0.4294770206022187</v>
+        <v>0.7624750499001997</v>
       </c>
       <c r="AI13">
-        <v>-0.3349814585908528</v>
+        <v>0.8082945408379179</v>
       </c>
       <c r="AJ13">
-        <v>0.4294770206022187</v>
+        <v>0.732824427480916</v>
       </c>
       <c r="AK13">
-        <v>-0.3349814585908528</v>
+        <v>0.7827338129496403</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>-0.045</v>
+      </c>
+      <c r="AQ13">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2019,7 +2049,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>First Al-Noor Modaraba (KASE:FANM)</t>
+          <t>Jahangir Siddiqui &amp; Co. Ltd. (KASE:JSCL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2028,112 +2058,109 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.0183</v>
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="E14">
+        <v>-0.07490000000000001</v>
       </c>
       <c r="G14">
-        <v>-0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>-0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>-0.1458333333333333</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>-0.1458333333333333</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>-0.013</v>
+        <v>6.66</v>
       </c>
       <c r="L14">
-        <v>-0.09027777777777778</v>
+        <v>0.07995198079231693</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>0.271</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.006545893719806764</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.04069069069069069</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.271</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.006545893719806764</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.04069069069069069</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>0.083</v>
+        <v>119.8</v>
       </c>
       <c r="V14">
-        <v>0.253822629969419</v>
+        <v>2.893719806763285</v>
       </c>
       <c r="W14">
-        <v>-0.008552631578947367</v>
+        <v>0.02582396277626987</v>
       </c>
       <c r="X14">
-        <v>0.06247469179582767</v>
+        <v>0.5487273095738441</v>
       </c>
       <c r="Y14">
-        <v>-0.07102732337477505</v>
+        <v>-0.5229033467975742</v>
       </c>
       <c r="Z14">
-        <v>0.1061164333087693</v>
+        <v>0.1503284487114705</v>
       </c>
       <c r="AA14">
-        <v>-0.0154753131908622</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06247469179582767</v>
+        <v>0.1601984465646006</v>
       </c>
       <c r="AC14">
-        <v>-0.07795000498668987</v>
+        <v>-0.1601984465646006</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>287.2</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>287.2</v>
       </c>
       <c r="AG14">
-        <v>-0.083</v>
+        <v>167.4</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.874010955569081</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.581023669836132</v>
       </c>
       <c r="AJ14">
-        <v>-0.3401639344262296</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="AK14">
-        <v>-0.06071689831748354</v>
+        <v>0.446995994659546</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.017</v>
-      </c>
-      <c r="AN14">
-        <v>-0</v>
-      </c>
-      <c r="AP14">
-        <v>5.533333333333334</v>
-      </c>
-      <c r="AQ14">
-        <v>1.235294117647059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2144,7 +2171,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EFG Hermes Pakistan Limited (KASE:EFGH)</t>
+          <t>AKD Hospitality Limited (KASE:AKDHL)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2152,23 +2179,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="K15">
-        <v>0.185</v>
-      </c>
-      <c r="L15">
-        <v>0.1468253968253968</v>
+        <v>-0.055</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2177,7 +2189,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2186,314 +2198,73 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.673</v>
+        <v>0.001</v>
       </c>
       <c r="V15">
-        <v>0.2913419913419913</v>
+        <v>0.0007692307692307692</v>
       </c>
       <c r="W15">
-        <v>0.2231604342581424</v>
+        <v>-0.3459119496855346</v>
       </c>
       <c r="X15">
-        <v>0.1128559332961005</v>
+        <v>0.1264557423724862</v>
       </c>
       <c r="Y15">
-        <v>0.1103045009620418</v>
+        <v>-0.4723676920580208</v>
       </c>
       <c r="Z15">
-        <v>0.5918271488961955</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>-0.1329787234042553</v>
       </c>
       <c r="AB15">
-        <v>0.08065057019097351</v>
+        <v>0.1259570614223711</v>
       </c>
       <c r="AC15">
-        <v>-0.08065057019097351</v>
+        <v>-0.2589357848266265</v>
       </c>
       <c r="AD15">
-        <v>3.46</v>
+        <v>0.034</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.46</v>
+        <v>0.034</v>
       </c>
       <c r="AG15">
-        <v>2.787</v>
+        <v>0.033</v>
       </c>
       <c r="AH15">
-        <v>0.5996533795493935</v>
+        <v>0.02548725637181409</v>
       </c>
       <c r="AI15">
-        <v>0.7740492170022372</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="AJ15">
-        <v>0.5467922307239553</v>
+        <v>0.02475618904726182</v>
       </c>
       <c r="AK15">
-        <v>0.7340005267316303</v>
+        <v>0.4125</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.067</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Jahangir Siddiqui &amp; Co. Ltd. (KASE:JSCL)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>0.114</v>
-      </c>
-      <c r="E16">
-        <v>0.0133</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>10.7</v>
-      </c>
-      <c r="L16">
-        <v>0.09744990892531875</v>
-      </c>
-      <c r="M16">
-        <v>0.117</v>
-      </c>
-      <c r="N16">
-        <v>0.001407942238267148</v>
-      </c>
-      <c r="O16">
-        <v>0.01093457943925234</v>
-      </c>
-      <c r="P16">
-        <v>0.117</v>
-      </c>
-      <c r="Q16">
-        <v>0.001407942238267148</v>
-      </c>
-      <c r="R16">
-        <v>0.01093457943925234</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>164.6</v>
-      </c>
-      <c r="V16">
-        <v>1.980746089049338</v>
-      </c>
-      <c r="W16">
-        <v>0.05061494796594134</v>
-      </c>
-      <c r="X16">
-        <v>0.2471692889699514</v>
-      </c>
-      <c r="Y16">
-        <v>-0.19655434100401</v>
-      </c>
-      <c r="Z16">
-        <v>0.3672240802675585</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.08811567353776428</v>
-      </c>
-      <c r="AC16">
-        <v>-0.08811567353776428</v>
-      </c>
-      <c r="AD16">
-        <v>456.3</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>456.3</v>
-      </c>
-      <c r="AG16">
-        <v>291.7</v>
-      </c>
-      <c r="AH16">
-        <v>0.8459399332591769</v>
-      </c>
-      <c r="AI16">
-        <v>0.6003157479279042</v>
-      </c>
-      <c r="AJ16">
-        <v>0.7782817502668089</v>
-      </c>
-      <c r="AK16">
-        <v>0.4898404701931151</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AKD Hospitality Limited (KASE:AKDHL)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>-0.208</v>
-      </c>
-      <c r="G17">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="H17">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="I17">
-        <v>-4</v>
-      </c>
-      <c r="J17">
-        <v>-2</v>
-      </c>
-      <c r="K17">
-        <v>-0.001</v>
-      </c>
-      <c r="L17">
-        <v>-0.06666666666666667</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0.002</v>
-      </c>
-      <c r="V17">
-        <v>0.000546448087431694</v>
-      </c>
-      <c r="W17">
-        <v>-0.006578947368421053</v>
-      </c>
-      <c r="X17">
-        <v>0.06275958714184575</v>
-      </c>
-      <c r="Y17">
-        <v>-0.06933853451026681</v>
-      </c>
-      <c r="Z17">
-        <v>0.09933774834437085</v>
-      </c>
-      <c r="AA17">
-        <v>-0.1986754966887417</v>
-      </c>
-      <c r="AB17">
-        <v>0.0627474331211446</v>
-      </c>
-      <c r="AC17">
-        <v>-0.2614229298098863</v>
-      </c>
-      <c r="AD17">
-        <v>0.031</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0.031</v>
-      </c>
-      <c r="AG17">
-        <v>0.029</v>
-      </c>
-      <c r="AH17">
-        <v>0.008398807911135193</v>
-      </c>
-      <c r="AI17">
-        <v>0.1631578947368421</v>
-      </c>
-      <c r="AJ17">
-        <v>0.007861208999728923</v>
-      </c>
-      <c r="AK17">
-        <v>0.1542553191489362</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>-0.5254237288135594</v>
-      </c>
-      <c r="AP17">
-        <v>-0.4915254237288135</v>
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>-1.416666666666667</v>
+      </c>
+      <c r="AP15">
+        <v>-1.375</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08160000000000001</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0004500000000000007</v>
+        <v>0.25</v>
       </c>
       <c r="G2">
-        <v>0.003199620300813407</v>
+        <v>0.004718477945944454</v>
       </c>
       <c r="H2">
-        <v>0.003199620300813407</v>
+        <v>0.004718477945944454</v>
       </c>
       <c r="I2">
-        <v>0.003649694767679743</v>
+        <v>0.005042700845738883</v>
       </c>
       <c r="J2">
-        <v>0.002769716018934144</v>
+        <v>0.004371126603614422</v>
       </c>
       <c r="K2">
-        <v>27.58</v>
+        <v>40.498</v>
       </c>
       <c r="L2">
-        <v>0.2256918872031554</v>
+        <v>0.2793697658696762</v>
       </c>
       <c r="M2">
-        <v>11.4524</v>
+        <v>9</v>
       </c>
       <c r="N2">
-        <v>0.06300004400827357</v>
+        <v>0.04861553752579324</v>
       </c>
       <c r="O2">
-        <v>0.4152429296591733</v>
+        <v>0.2222331967010717</v>
       </c>
       <c r="P2">
-        <v>11.4524</v>
+        <v>9</v>
       </c>
       <c r="Q2">
-        <v>0.06300004400827357</v>
+        <v>0.04861553752579324</v>
       </c>
       <c r="R2">
-        <v>0.4152429296591733</v>
+        <v>0.2222331967010717</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>150.255</v>
+        <v>301.349</v>
       </c>
       <c r="V2">
-        <v>0.8265578928838622</v>
+        <v>1.627804846428919</v>
       </c>
       <c r="W2">
-        <v>0.01138686131386861</v>
+        <v>0.01232528409090909</v>
       </c>
       <c r="X2">
-        <v>0.14281155891357</v>
+        <v>0.122751979532677</v>
       </c>
       <c r="Y2">
-        <v>-0.1314246975997014</v>
+        <v>-0.1104266954417679</v>
       </c>
       <c r="Z2">
-        <v>0.1453636649124977</v>
+        <v>0.2209796691143405</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1346535148184695</v>
+        <v>0.1210940332416815</v>
       </c>
       <c r="AC2">
-        <v>-0.1346535148184695</v>
+        <v>-0.1210940332416815</v>
       </c>
       <c r="AD2">
-        <v>384.567</v>
+        <v>474.983</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>384.567</v>
+        <v>474.983</v>
       </c>
       <c r="AG2">
-        <v>234.312</v>
+        <v>173.634</v>
       </c>
       <c r="AH2">
-        <v>0.6790259044302914</v>
+        <v>0.7195523769559269</v>
       </c>
       <c r="AI2">
-        <v>0.4699194005630719</v>
+        <v>0.5151318622086825</v>
       </c>
       <c r="AJ2">
-        <v>0.5631200492194109</v>
+        <v>0.4839837217081058</v>
       </c>
       <c r="AK2">
-        <v>0.3507071408579088</v>
+        <v>0.2797335962572015</v>
       </c>
       <c r="AL2">
-        <v>0.458</v>
+        <v>0.712</v>
       </c>
       <c r="AM2">
-        <v>0.41</v>
+        <v>0.631</v>
       </c>
       <c r="AN2">
-        <v>789.6652977412731</v>
+        <v>627.4544253632761</v>
       </c>
       <c r="AO2">
-        <v>0.9737991266375544</v>
+        <v>1.026685393258427</v>
       </c>
       <c r="AP2">
-        <v>481.1334702258727</v>
+        <v>229.3712021136064</v>
       </c>
       <c r="AQ2">
-        <v>1.08780487804878</v>
+        <v>1.158478605388273</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Al-Noor Modaraba (KASE:FANM)</t>
+          <t>First Credit and Investment Bank Limited (KASE:FCIBL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.008880000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="E3">
-        <v>-0.053</v>
+        <v>0.119</v>
       </c>
       <c r="G3">
-        <v>0.3152173913043478</v>
+        <v>0.6628571428571428</v>
       </c>
       <c r="H3">
-        <v>0.3152173913043478</v>
+        <v>0.6628571428571428</v>
       </c>
       <c r="I3">
-        <v>0.2826086956521739</v>
+        <v>0.7028571428571428</v>
       </c>
       <c r="J3">
-        <v>0.1994884910485933</v>
+        <v>0.3544844720496894</v>
       </c>
       <c r="K3">
-        <v>0.011</v>
+        <v>0.058</v>
       </c>
       <c r="L3">
-        <v>0.05978260869565217</v>
+        <v>0.05523809523809524</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,70 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.465</v>
+        <v>0.493</v>
       </c>
       <c r="V3">
-        <v>1.01528384279476</v>
+        <v>0.3286666666666667</v>
       </c>
       <c r="W3">
-        <v>0.006874999999999999</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="X3">
-        <v>0.1248577167703053</v>
+        <v>0.252414873588621</v>
       </c>
       <c r="Y3">
-        <v>-0.1179827167703053</v>
+        <v>-0.2342330554068028</v>
       </c>
       <c r="Z3">
-        <v>0.149959250203749</v>
+        <v>0.1214855952794169</v>
       </c>
       <c r="AA3">
-        <v>0.02991514454192434</v>
+        <v>0.04306475710426633</v>
       </c>
       <c r="AB3">
-        <v>0.1248577167703053</v>
+        <v>0.1530872591841139</v>
       </c>
       <c r="AC3">
-        <v>-0.094942572228381</v>
+        <v>-0.1100225020798476</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AG3">
-        <v>-0.465</v>
+        <v>3.457</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.7247706422018348</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.6095679012345679</v>
       </c>
       <c r="AJ3">
-        <v>66.42857142857137</v>
+        <v>0.6973976195279402</v>
       </c>
       <c r="AK3">
-        <v>-0.607843137254902</v>
+        <v>0.5774177384332722</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="AM3">
-        <v>-0.003</v>
+        <v>0.712</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>5.176933158584535</v>
+      </c>
+      <c r="AO3">
+        <v>1.036516853932584</v>
       </c>
       <c r="AP3">
-        <v>-8.017241379310345</v>
+        <v>4.530799475753605</v>
       </c>
       <c r="AQ3">
-        <v>-17.33333333333333</v>
+        <v>1.036516853932584</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Credit and Investment Bank Limited (KASE:FCIBL)</t>
+          <t>Security Investment Bank Limited (KASE:SIBL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,28 +853,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.137</v>
+        <v>0.0476</v>
       </c>
       <c r="E4">
-        <v>0.0429</v>
+        <v>0.257</v>
       </c>
       <c r="G4">
-        <v>0.4870748299319728</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.4870748299319728</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.5700680272108843</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.3126179504059688</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.034</v>
+        <v>0.227</v>
       </c>
       <c r="L4">
-        <v>0.04625850340136055</v>
+        <v>0.8284671532846715</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,73 +898,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.327</v>
+        <v>0.02</v>
       </c>
       <c r="V4">
-        <v>0.2069620253164557</v>
+        <v>0.02254791431792559</v>
       </c>
       <c r="W4">
-        <v>0.007798165137614678</v>
+        <v>0.07516556291390729</v>
       </c>
       <c r="X4">
-        <v>0.3483790193538364</v>
+        <v>0.1132389151778213</v>
       </c>
       <c r="Y4">
-        <v>-0.3405808542162217</v>
+        <v>-0.03807335226391396</v>
       </c>
       <c r="Z4">
-        <v>0.1180154142581888</v>
+        <v>0.09121171770972038</v>
       </c>
       <c r="AA4">
-        <v>0.03689373692170633</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1587312738620833</v>
+        <v>0.1132389151778213</v>
       </c>
       <c r="AC4">
-        <v>-0.1218375369403769</v>
+        <v>-0.1132389151778213</v>
       </c>
       <c r="AD4">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>5.453</v>
+        <v>-0.02</v>
       </c>
       <c r="AH4">
-        <v>0.7853260869565217</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.6443701226309921</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.7753448030712357</v>
+        <v>-0.02306805074971165</v>
       </c>
       <c r="AK4">
-        <v>0.6309151914844383</v>
+        <v>-0.007692307692307692</v>
       </c>
       <c r="AL4">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.458</v>
-      </c>
-      <c r="AN4">
-        <v>12.75938189845475</v>
-      </c>
-      <c r="AO4">
-        <v>0.9148471615720524</v>
-      </c>
-      <c r="AP4">
-        <v>12.03752759381898</v>
-      </c>
-      <c r="AQ4">
-        <v>0.9148471615720524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +972,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.249</v>
+        <v>0.0299</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,61 +987,58 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.064</v>
+        <v>-0.01</v>
       </c>
       <c r="L5">
-        <v>-2.56</v>
+        <v>-0.2127659574468085</v>
       </c>
       <c r="M5">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1300813008130081</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1300813008130081</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="V5">
-        <v>0.08130081300813008</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="W5">
-        <v>-0.07729468599033817</v>
+        <v>-0.0193050193050193</v>
       </c>
       <c r="X5">
-        <v>0.1248577167703053</v>
+        <v>0.1132389151778213</v>
       </c>
       <c r="Y5">
-        <v>-0.2021524027606435</v>
+        <v>-0.1325439344828405</v>
       </c>
       <c r="Z5">
-        <v>0.03075030750307503</v>
+        <v>0.09251968503937008</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1248577167703053</v>
+        <v>0.1132389151778213</v>
       </c>
       <c r="AC5">
-        <v>-0.1248577167703053</v>
+        <v>-0.1132389151778213</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1062,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1071,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.08849557522123894</v>
+        <v>-0.225</v>
       </c>
       <c r="AK5">
-        <v>-0.01968503937007874</v>
+        <v>-0.0712401055408971</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AKD Securities Limited (KASE:AKDSL)</t>
+          <t>Invest Capital Investment Bank Limited (KASE:ICIBL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,10 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.063</v>
+        <v>0.171</v>
       </c>
       <c r="E6">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,85 +1106,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.706</v>
+        <v>0.349</v>
       </c>
       <c r="L6">
-        <v>0.2417808219178082</v>
+        <v>0.695219123505976</v>
       </c>
       <c r="M6">
-        <v>1.6734</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03669736842105263</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>2.370254957507082</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>1.6734</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03669736842105263</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>2.370254957507082</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>4.28</v>
+        <v>0.057</v>
       </c>
       <c r="V6">
-        <v>0.09385964912280702</v>
+        <v>0.04160583941605839</v>
       </c>
       <c r="W6">
-        <v>0.1281306715063521</v>
+        <v>0.163849765258216</v>
       </c>
       <c r="X6">
-        <v>0.1259765614498509</v>
+        <v>0.1162865639021453</v>
       </c>
       <c r="Y6">
-        <v>0.002154110056501207</v>
+        <v>0.04756320135607063</v>
       </c>
       <c r="Z6">
-        <v>41.71428571428607</v>
+        <v>0.1832116788321168</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1255848260087029</v>
+        <v>0.116133163132746</v>
       </c>
       <c r="AC6">
-        <v>-0.1255848260087029</v>
+        <v>-0.116133163132746</v>
       </c>
       <c r="AD6">
-        <v>0.835</v>
+        <v>0.079</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.835</v>
+        <v>0.079</v>
       </c>
       <c r="AG6">
-        <v>-3.445</v>
+        <v>0.022</v>
       </c>
       <c r="AH6">
-        <v>0.01798212555184667</v>
+        <v>0.05452035886818495</v>
       </c>
       <c r="AI6">
-        <v>0.1435941530524505</v>
+        <v>0.03763696998570747</v>
       </c>
       <c r="AJ6">
-        <v>-0.08172221563278378</v>
+        <v>0.01580459770114942</v>
       </c>
       <c r="AK6">
-        <v>-2.244299674267101</v>
+        <v>0.01077375122428991</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Escorts Investment Bank Limited (KASE:ESBL)</t>
+          <t>AKD Securities Limited (KASE:AKDSL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1221,9 +1206,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.537</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1237,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-0.864</v>
+        <v>0.207</v>
       </c>
       <c r="L7">
-        <v>-2.420168067226891</v>
+        <v>0.0672077922077922</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1249,7 +1231,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1258,61 +1240,61 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.179</v>
+        <v>1.31</v>
       </c>
       <c r="V7">
-        <v>0.07047244094488189</v>
+        <v>0.03156626506024097</v>
       </c>
       <c r="W7">
-        <v>-0.1774127310061601</v>
+        <v>0.00646875</v>
       </c>
       <c r="X7">
-        <v>0.1306069821083971</v>
+        <v>0.116257188974682</v>
       </c>
       <c r="Y7">
-        <v>-0.3080197131145572</v>
+        <v>-0.109788438974682</v>
       </c>
       <c r="Z7">
-        <v>0.07344167866694096</v>
+        <v>0.08396946564885496</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1283352235971319</v>
+        <v>0.1162091473387644</v>
       </c>
       <c r="AC7">
-        <v>-0.1283352235971319</v>
+        <v>-0.1162091473387644</v>
       </c>
       <c r="AD7">
-        <v>0.239</v>
+        <v>2.37</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.239</v>
+        <v>2.37</v>
       </c>
       <c r="AG7">
-        <v>0.06</v>
+        <v>1.06</v>
       </c>
       <c r="AH7">
-        <v>0.08600215905001798</v>
+        <v>0.05402325051287896</v>
       </c>
       <c r="AI7">
-        <v>0.07916528651871481</v>
+        <v>0.07413199874882702</v>
       </c>
       <c r="AJ7">
-        <v>0.02307692307692307</v>
+        <v>0.02490601503759398</v>
       </c>
       <c r="AK7">
-        <v>0.02112676056338028</v>
+        <v>0.03457273320287019</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1338,10 +1320,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.07629999999999999</v>
-      </c>
-      <c r="E8">
-        <v>-0.274</v>
+        <v>0.0528</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,85 +1335,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.156</v>
+        <v>0.483</v>
       </c>
       <c r="L8">
-        <v>0.06473029045643153</v>
+        <v>0.1677083333333333</v>
       </c>
       <c r="M8">
-        <v>0.601</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.04926229508196722</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>3.852564102564103</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.601</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.04926229508196722</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>3.852564102564103</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>6.24</v>
+        <v>4.87</v>
       </c>
       <c r="V8">
-        <v>0.5114754098360657</v>
+        <v>0.3141935483870968</v>
       </c>
       <c r="W8">
-        <v>0.01138686131386861</v>
+        <v>0.04984520123839009</v>
       </c>
       <c r="X8">
-        <v>0.1392314716443095</v>
+        <v>0.1180808064218393</v>
       </c>
       <c r="Y8">
-        <v>-0.1278446103304409</v>
+        <v>-0.06823560518344918</v>
       </c>
       <c r="Z8">
-        <v>1.004166666666667</v>
+        <v>0.4556962025316457</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1325583649376931</v>
+        <v>0.1176940927125296</v>
       </c>
       <c r="AC8">
-        <v>-0.1325583649376931</v>
+        <v>-0.1176940927125296</v>
       </c>
       <c r="AD8">
-        <v>2.87</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.87</v>
+        <v>1.42</v>
       </c>
       <c r="AG8">
-        <v>-3.37</v>
+        <v>-3.45</v>
       </c>
       <c r="AH8">
-        <v>0.1904445919044459</v>
+        <v>0.08392434988179667</v>
       </c>
       <c r="AI8">
-        <v>0.2285031847133758</v>
+        <v>0.1480709071949948</v>
       </c>
       <c r="AJ8">
-        <v>-0.3816534541336354</v>
+        <v>-0.2863070539419087</v>
       </c>
       <c r="AK8">
-        <v>-0.5332278481012659</v>
+        <v>-0.7309322033898306</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dawood Equities Limited (KASE:DEL)</t>
+          <t>Escorts Investment Bank Limited (KASE:ESBL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1459,12 +1435,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0935</v>
-      </c>
-      <c r="E9">
-        <v>0.598</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1478,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.024</v>
+        <v>-0.14</v>
       </c>
       <c r="L9">
-        <v>0.04771371769383698</v>
+        <v>-0.3763440860215054</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1490,7 +1460,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1499,61 +1469,61 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.344</v>
+        <v>0.32</v>
       </c>
       <c r="V9">
-        <v>0.5434439178515007</v>
+        <v>0.1367521367521368</v>
       </c>
       <c r="W9">
-        <v>0.01411764705882353</v>
+        <v>-0.05035971223021583</v>
       </c>
       <c r="X9">
-        <v>0.14281155891357</v>
+        <v>0.1181852856568808</v>
       </c>
       <c r="Y9">
-        <v>-0.1286939118547465</v>
+        <v>-0.1685449978870966</v>
       </c>
       <c r="Z9">
-        <v>0.3120347394540943</v>
+        <v>0.1309859154929577</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1346535148184695</v>
+        <v>0.117782000133793</v>
       </c>
       <c r="AC9">
-        <v>-0.1346535148184695</v>
+        <v>-0.117782000133793</v>
       </c>
       <c r="AD9">
-        <v>0.186</v>
+        <v>0.219</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.186</v>
+        <v>0.219</v>
       </c>
       <c r="AG9">
-        <v>-0.158</v>
+        <v>-0.101</v>
       </c>
       <c r="AH9">
-        <v>0.2271062271062271</v>
+        <v>0.08558030480656507</v>
       </c>
       <c r="AI9">
-        <v>0.1313559322033898</v>
+        <v>0.09609477841158404</v>
       </c>
       <c r="AJ9">
-        <v>-0.3326315789473683</v>
+        <v>-0.04510942384993301</v>
       </c>
       <c r="AK9">
-        <v>-0.1473880597014925</v>
+        <v>-0.0515569167942828</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Invest Capital Investment Bank Limited (KASE:ICIBL)</t>
+          <t>First National Equities Limited (KASE:FNEL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,7 +1549,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.39</v>
+        <v>-0.107</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1594,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.235</v>
+        <v>-0.304</v>
       </c>
       <c r="L10">
-        <v>0.5581947743467933</v>
+        <v>-14.47619047619047</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1606,7 +1576,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1615,61 +1585,61 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.093</v>
+        <v>0.981</v>
       </c>
       <c r="V10">
-        <v>0.0636986301369863</v>
+        <v>0.1950298210735586</v>
       </c>
       <c r="W10">
-        <v>0.0914396887159533</v>
+        <v>-0.05477477477477478</v>
       </c>
       <c r="X10">
-        <v>0.1542782566138413</v>
+        <v>0.1273186734084732</v>
       </c>
       <c r="Y10">
-        <v>-0.06283856789788801</v>
+        <v>-0.1820934481832479</v>
       </c>
       <c r="Z10">
-        <v>0.1601978691019787</v>
+        <v>0.003392568659127626</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1379995951173265</v>
+        <v>0.12440606634957</v>
       </c>
       <c r="AC10">
-        <v>-0.1379995951173265</v>
+        <v>-0.12440606634957</v>
       </c>
       <c r="AD10">
-        <v>0.703</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.703</v>
+        <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>0.61</v>
+        <v>0.3590000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.3250115580212667</v>
+        <v>0.2103610675039247</v>
       </c>
       <c r="AI10">
-        <v>0.2481468408048006</v>
+        <v>0.2458715596330275</v>
       </c>
       <c r="AJ10">
-        <v>0.2946859903381643</v>
+        <v>0.06661718315086289</v>
       </c>
       <c r="AK10">
-        <v>0.2226277372262774</v>
+        <v>0.08033117028417992</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,7 +1656,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arif Habib Limited (KASE:AHL)</t>
+          <t>Dawood Equities Limited (KASE:DEL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1695,10 +1665,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0301</v>
-      </c>
-      <c r="E11">
-        <v>-0.0126</v>
+        <v>0.0147</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1713,85 +1680,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>4.04</v>
+        <v>-0.075</v>
       </c>
       <c r="L11">
-        <v>0.5706214689265536</v>
+        <v>-0.3768844221105527</v>
       </c>
       <c r="M11">
-        <v>2.89</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.2580357142857143</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.7153465346534653</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.89</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.2580357142857143</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.7153465346534653</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>5.26</v>
+        <v>0.036</v>
       </c>
       <c r="V11">
-        <v>0.4696428571428571</v>
+        <v>0.05669291338582676</v>
       </c>
       <c r="W11">
-        <v>0.12625</v>
+        <v>-0.06097560975609756</v>
       </c>
       <c r="X11">
-        <v>0.1903230513134305</v>
+        <v>0.1294689432193478</v>
       </c>
       <c r="Y11">
-        <v>-0.06407305131343047</v>
+        <v>-0.1904445529754453</v>
       </c>
       <c r="Z11">
-        <v>0.2964824120603015</v>
+        <v>0.1856343283582089</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1457724292326146</v>
+        <v>0.1257108418348862</v>
       </c>
       <c r="AC11">
-        <v>-0.1457724292326146</v>
+        <v>-0.1257108418348862</v>
       </c>
       <c r="AD11">
-        <v>12</v>
+        <v>0.195</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>12</v>
+        <v>0.195</v>
       </c>
       <c r="AG11">
-        <v>6.74</v>
+        <v>0.159</v>
       </c>
       <c r="AH11">
-        <v>0.5172413793103449</v>
+        <v>0.2349397590361446</v>
       </c>
       <c r="AI11">
-        <v>0.3183023872679045</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="AJ11">
-        <v>0.3756967670011149</v>
+        <v>0.2002518891687657</v>
       </c>
       <c r="AK11">
-        <v>0.2077681874229347</v>
+        <v>0.1522988505747127</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1808,7 +1772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arif Habib Corporation Limited (KASE:AHCL)</t>
+          <t>Arif Habib Limited (KASE:AHL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1817,10 +1781,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.12</v>
+        <v>0.0771</v>
       </c>
       <c r="E12">
-        <v>0.0117</v>
+        <v>-0.18</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1835,28 +1799,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>17</v>
+        <v>0.885</v>
       </c>
       <c r="L12">
-        <v>0.7172995780590717</v>
+        <v>0.2610619469026549</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="N12">
-        <v>0.0966183574879227</v>
+        <v>0.1336633663366337</v>
       </c>
       <c r="O12">
-        <v>0.3529411764705883</v>
+        <v>1.525423728813559</v>
       </c>
       <c r="P12">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="Q12">
-        <v>0.0966183574879227</v>
+        <v>0.1336633663366337</v>
       </c>
       <c r="R12">
-        <v>0.3529411764705883</v>
+        <v>1.525423728813559</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1865,55 +1829,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>12.7</v>
+        <v>4.04</v>
       </c>
       <c r="V12">
-        <v>0.2045088566827697</v>
+        <v>0.4</v>
       </c>
       <c r="W12">
-        <v>0.08952080042127435</v>
+        <v>0.03782051282051282</v>
       </c>
       <c r="X12">
-        <v>0.1946171274707948</v>
+        <v>0.162113590634277</v>
       </c>
       <c r="Y12">
-        <v>-0.1050963270495205</v>
+        <v>-0.1242930778137642</v>
       </c>
       <c r="Z12">
-        <v>0.09922960978060627</v>
+        <v>0.09570863918690005</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1478512322057711</v>
+        <v>0.138744051252238</v>
       </c>
       <c r="AC12">
-        <v>-0.1478512322057711</v>
+        <v>-0.138744051252238</v>
       </c>
       <c r="AD12">
-        <v>70.90000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>70.90000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="AG12">
-        <v>58.2</v>
+        <v>5.3</v>
       </c>
       <c r="AH12">
-        <v>0.5330827067669174</v>
+        <v>0.4804526748971194</v>
       </c>
       <c r="AI12">
-        <v>0.2891517128874388</v>
+        <v>0.3428781204111601</v>
       </c>
       <c r="AJ12">
-        <v>0.483790523690773</v>
+        <v>0.3441558441558442</v>
       </c>
       <c r="AK12">
-        <v>0.2503225806451613</v>
+        <v>0.228448275862069</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1930,7 +1894,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EFG Hermes Pakistan Limited (KASE:EFGH)</t>
+          <t>Arif Habib Corporation Limited (KASE:AHCL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1938,6 +1902,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.303</v>
+      </c>
+      <c r="E13">
+        <v>0.243</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1951,28 +1921,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.303</v>
+        <v>13.8</v>
       </c>
       <c r="L13">
-        <v>-0.5343915343915344</v>
+        <v>0.4928571428571429</v>
       </c>
       <c r="M13">
-        <v>0.001</v>
+        <v>5.68</v>
       </c>
       <c r="N13">
-        <v>0.0008403361344537816</v>
+        <v>0.1059701492537313</v>
       </c>
       <c r="O13">
-        <v>-0.0033003300330033</v>
+        <v>0.4115942028985507</v>
       </c>
       <c r="P13">
-        <v>0.001</v>
+        <v>5.68</v>
       </c>
       <c r="Q13">
-        <v>0.0008403361344537816</v>
+        <v>0.1059701492537313</v>
       </c>
       <c r="R13">
-        <v>-0.0033003300330033</v>
+        <v>0.4115942028985507</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1981,64 +1951,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.556</v>
+        <v>7.85</v>
       </c>
       <c r="V13">
-        <v>0.4672268907563026</v>
+        <v>0.146455223880597</v>
       </c>
       <c r="W13">
-        <v>-0.3</v>
+        <v>0.09249329758713137</v>
       </c>
       <c r="X13">
-        <v>0.3209969935975508</v>
+        <v>0.171809564594042</v>
       </c>
       <c r="Y13">
-        <v>-0.6209969935975508</v>
+        <v>-0.07931626700691063</v>
       </c>
       <c r="Z13">
-        <v>0.1493284171714511</v>
+        <v>0.1386001386001386</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1577456375497414</v>
+        <v>0.1389749463503476</v>
       </c>
       <c r="AC13">
-        <v>-0.1577456375497414</v>
+        <v>-0.1389749463503476</v>
       </c>
       <c r="AD13">
-        <v>3.82</v>
+        <v>59.4</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>3.82</v>
+        <v>59.4</v>
       </c>
       <c r="AG13">
-        <v>3.264</v>
+        <v>51.55</v>
       </c>
       <c r="AH13">
-        <v>0.7624750499001997</v>
+        <v>0.5256637168141592</v>
       </c>
       <c r="AI13">
-        <v>0.8082945408379179</v>
+        <v>0.2996972754793138</v>
       </c>
       <c r="AJ13">
-        <v>0.732824427480916</v>
+        <v>0.4902520209224916</v>
       </c>
       <c r="AK13">
-        <v>0.7827338129496403</v>
+        <v>0.2708169162069871</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.045</v>
-      </c>
-      <c r="AQ13">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2049,7 +2016,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jahangir Siddiqui &amp; Co. Ltd. (KASE:JSCL)</t>
+          <t>EFG Hermes Pakistan Limited (KASE:EFGH)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2058,10 +2025,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.08160000000000001</v>
-      </c>
-      <c r="E14">
-        <v>-0.07490000000000001</v>
+        <v>-0.0406</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2076,91 +2040,91 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>6.66</v>
+        <v>-0.469</v>
       </c>
       <c r="L14">
-        <v>0.07995198079231693</v>
+        <v>-1.387573964497041</v>
       </c>
       <c r="M14">
-        <v>0.271</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.006545893719806764</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.04069069069069069</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>0.271</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.006545893719806764</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.04069069069069069</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>119.8</v>
+        <v>0.344</v>
       </c>
       <c r="V14">
-        <v>2.893719806763285</v>
+        <v>0.3751363140676117</v>
       </c>
       <c r="W14">
-        <v>0.02582396277626987</v>
+        <v>-0.5176600441501104</v>
       </c>
       <c r="X14">
-        <v>0.5487273095738441</v>
+        <v>0.2786524129508271</v>
       </c>
       <c r="Y14">
-        <v>-0.5229033467975742</v>
+        <v>-0.7963124571009375</v>
       </c>
       <c r="Z14">
-        <v>0.1503284487114705</v>
+        <v>0.08105515587529977</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.1601984465646006</v>
+        <v>0.1549063031289015</v>
       </c>
       <c r="AC14">
-        <v>-0.1601984465646006</v>
+        <v>-0.1549063031289015</v>
       </c>
       <c r="AD14">
-        <v>287.2</v>
+        <v>2.87</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>287.2</v>
+        <v>2.87</v>
       </c>
       <c r="AG14">
-        <v>167.4</v>
+        <v>2.526</v>
       </c>
       <c r="AH14">
-        <v>0.874010955569081</v>
+        <v>0.7578558225508318</v>
       </c>
       <c r="AI14">
-        <v>0.581023669836132</v>
+        <v>0.8660229330114665</v>
       </c>
       <c r="AJ14">
-        <v>0.8017241379310345</v>
+        <v>0.7336625036305547</v>
       </c>
       <c r="AK14">
-        <v>0.446995994659546</v>
+        <v>0.8505050505050505</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.081</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2171,100 +2135,240 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Jahangir Siddiqui &amp; Co. Ltd. (KASE:JSCL)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.179</v>
+      </c>
+      <c r="E15">
+        <v>0.4379999999999999</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>25.5</v>
+      </c>
+      <c r="L15">
+        <v>0.2433206106870229</v>
+      </c>
+      <c r="M15">
+        <v>1.97</v>
+      </c>
+      <c r="N15">
+        <v>0.03924302788844621</v>
+      </c>
+      <c r="O15">
+        <v>0.07725490196078431</v>
+      </c>
+      <c r="P15">
+        <v>1.97</v>
+      </c>
+      <c r="Q15">
+        <v>0.03924302788844621</v>
+      </c>
+      <c r="R15">
+        <v>0.07725490196078431</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>281</v>
+      </c>
+      <c r="V15">
+        <v>5.597609561752988</v>
+      </c>
+      <c r="W15">
+        <v>0.147313691507799</v>
+      </c>
+      <c r="X15">
+        <v>0.5278399471676313</v>
+      </c>
+      <c r="Y15">
+        <v>-0.3805262556598323</v>
+      </c>
+      <c r="Z15">
+        <v>0.3026190407438422</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.1603225270462472</v>
+      </c>
+      <c r="AC15">
+        <v>-0.1603225270462472</v>
+      </c>
+      <c r="AD15">
+        <v>393.8</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>393.8</v>
+      </c>
+      <c r="AG15">
+        <v>112.8</v>
+      </c>
+      <c r="AH15">
+        <v>0.886936936936937</v>
+      </c>
+      <c r="AI15">
+        <v>0.6237921748772375</v>
+      </c>
+      <c r="AJ15">
+        <v>0.6920245398773007</v>
+      </c>
+      <c r="AK15">
+        <v>0.3220097059663146</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>AKD Hospitality Limited (KASE:AKDHL)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="K15">
-        <v>-0.055</v>
-      </c>
-      <c r="M15">
-        <v>-0</v>
-      </c>
-      <c r="N15">
-        <v>-0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>-0</v>
-      </c>
-      <c r="Q15">
-        <v>-0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="U15">
+      <c r="D16">
+        <v>-0.146</v>
+      </c>
+      <c r="G16">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="H16">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="I16">
+        <v>-0.7777777777777779</v>
+      </c>
+      <c r="J16">
+        <v>-0.7777777777777779</v>
+      </c>
+      <c r="K16">
+        <v>-0.013</v>
+      </c>
+      <c r="L16">
+        <v>-1.444444444444444</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
         <v>0.001</v>
       </c>
-      <c r="V15">
-        <v>0.0007692307692307692</v>
-      </c>
-      <c r="W15">
-        <v>-0.3459119496855346</v>
-      </c>
-      <c r="X15">
-        <v>0.1264557423724862</v>
-      </c>
-      <c r="Y15">
-        <v>-0.4723676920580208</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>-0.1329787234042553</v>
-      </c>
-      <c r="AB15">
-        <v>0.1259570614223711</v>
-      </c>
-      <c r="AC15">
-        <v>-0.2589357848266265</v>
-      </c>
-      <c r="AD15">
-        <v>0.034</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0.034</v>
-      </c>
-      <c r="AG15">
-        <v>0.033</v>
-      </c>
-      <c r="AH15">
-        <v>0.02548725637181409</v>
-      </c>
-      <c r="AI15">
-        <v>0.4197530864197531</v>
-      </c>
-      <c r="AJ15">
-        <v>0.02475618904726182</v>
-      </c>
-      <c r="AK15">
-        <v>0.4125</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>-1.416666666666667</v>
-      </c>
-      <c r="AP15">
-        <v>-1.375</v>
+      <c r="V16">
+        <v>0.0007142857142857144</v>
+      </c>
+      <c r="W16">
+        <v>-0.2765957446808511</v>
+      </c>
+      <c r="X16">
+        <v>0.1132389151778213</v>
+      </c>
+      <c r="Y16">
+        <v>-0.3898346598586723</v>
+      </c>
+      <c r="Z16">
+        <v>0.1125</v>
+      </c>
+      <c r="AA16">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="AB16">
+        <v>0.1132389151778213</v>
+      </c>
+      <c r="AC16">
+        <v>-0.2007389151778212</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>-0.001</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.0007147962830593281</v>
+      </c>
+      <c r="AK16">
+        <v>-0.03125</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>-0</v>
+      </c>
+      <c r="AP16">
+        <v>0.1666666666666667</v>
       </c>
     </row>
   </sheetData>
